--- a/deploy/ppf/site_assets/sablona_import_aktivit.xlsx
+++ b/deploy/ppf/site_assets/sablona_import_aktivit.xlsx
@@ -583,18 +583,30 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="8">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>=Cis_Procesy</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>=INDIRECT("P_"&amp;SUBSTITUTE(LEFT($B2,5),"-","_"))</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>=Cis_Utvary</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>"pracovní,schváleno"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -827,7 +839,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Útvary, které se na činnosti podílejí. Více útvarů oddělte '; '.</t>
+          <t>Útvary, které se na činnosti podílejí. Více oddělte '; '. Na rozdíl od sloupce vlevo tu smí být i volný popis ('věcně příslušné útvary', 'podřízené služební úřady') — import tenhle sloupec proti číselníku nekontroluje.</t>
         </is>
       </c>
     </row>
